--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0215.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0215.xlsx
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Total Points: {0}</t>
+          <t>Tổng Điểm: {0}</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Thời Gian Kỷ Lục 3-Star: {0}</t>
+          <t>Thời Gian Ghi Nhận 3 Sao: {0}</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>&lt;color=#5d1f2f&gt;Lv. {0}/&lt;/color&gt;&lt;color=#a87361&gt;{1}&lt;/color&gt;</t>
+          <t>&lt;color=#5d1f2f&gt;Cấp {0}/&lt;/color&gt;&lt;color=#a87361&gt;{1}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Trao cho đội kỹ năng Lao Nhanh của Loong khi nó Lao Vút, kéo dài trong &lt;color=#f97507&gt;{0}s&lt;/color&gt;.
+          <t>Trao cho đội kỹ năng Lao Nhanh của Loong khi nó Lao Vút, kéo dài trong &lt;color=#f97507&gt;{0} giây&lt;/color&gt;.
 Chỉ có hiệu lực khi ở vị trí Đội Trưởng.</t>
         </is>
       </c>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Total Points: {0}</t>
+          <t>Tổng Điểm: {0}</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Hừ. Ta chưa xong đâu.</t>
+          <t>Hừ. Tao chưa xong đâu.</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>&lt;color=#ffe65a&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>&lt;color=#d5aa29&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nhanh lên! Dự Án Công Cụ Hóa Nhiên Liệu F.U.E.L!</t>
+          <t>Tăng tốc nào! Dự án Công Cụ Hóa Nhiên Liệu F.U.E.L.!</t>
         </is>
       </c>
     </row>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nhanh lên! Dự Án Công Cụ Hóa Nhiên Liệu F.U.E.L!</t>
+          <t>Tăng tốc nào! Dự án Công Cụ Hóa Nhiên Liệu F.U.E.L.!</t>
         </is>
       </c>
     </row>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Đánh bại "Kẻ Gào Thét Hoang Mạc" tại Vịnh Wuming.</t>
+          <t>Đánh bại "Kẻ Gào Thét Hoang Mạc" tại Wuming Bay.</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Đánh bại "Người Bảo Vệ Obelisk" tại Cao nguyên Desorock.</t>
+          <t>Đánh bại "Người Bảo Vệ Obelisk" tại Desorock Highland.</t>
         </is>
       </c>
     </row>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Đánh bại "Cò Đôi" tại Đầm Lầy Whining Aix.</t>
+          <t>Đánh bại "Cò Đôi" tại Whining Aix's Mire.</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Đánh bại "Carapace: Engine Zero" tại Đồng Bằng Trung Tâm.</t>
+          <t>Đánh bại "Carapace: Engine Zero" tại Central Plains.</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Đánh bại "Autopuppet Scout-01" tại Đồng Bằng Trung Tâm.</t>
+          <t>Đánh bại "Autopuppet Scout-01" tại Central Plains.</t>
         </is>
       </c>
     </row>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Đánh bại "Nhà hát Illuminator" tại Cao nguyên Desorock.</t>
+          <t>Đánh bại "Nhà hát Illuminator" tại Desorock Highland.</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Echo: Clang Bang một lần</t>
+          <t>Hoàn thành Thử thách Echo: Clang Bang once.</t>
         </is>
       </c>
     </row>
@@ -19645,7 +19645,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Tiêu diệt Construct: Vảy Bảo Hộ đang lang thang trên Núi Firmament.</t>
+          <t>Tiêu diệt Construct: Protective Scales roaming in Mt. Firmament.</t>
         </is>
       </c>
     </row>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách Echo: Tiếng Vang Chiến Trường.</t>
+          <t>Hoàn thành tất cả thử thách Echo: Clang Bang.</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Hoàn thành Thư Viện Tro Tàn</t>
+          <t>Hoàn thành Ashened Gallery</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách Echo: Bay Lượn ở khu vực Ragunna.</t>
+          <t>Hoàn thành tất cả thử thách Echo: Flight in the Ragunna region.</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Hoàn thành mọi mục tiêu của Dream Patrol: Twin Swords of Light trong một lần thử.</t>
+          <t>Hoàn thành mọi mục tiêu của Dream Patrol: Twin Kiếm đơn of Light trong một lần thử.</t>
         </is>
       </c>
     </row>
